--- a/Assets/StreamingAssets/pages.xlsx
+++ b/Assets/StreamingAssets/pages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Work\Encore\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766DB1C1-9B26-4DCC-BBB4-183DEEF2B1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157E0B41-2878-476C-8612-7A0216979750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6240" yWindow="420" windowWidth="19245" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="51">
   <si>
     <t>ID (уникальный)</t>
   </si>
@@ -184,6 +184,10 @@
   </si>
   <si>
     <t>private_residences</t>
+  </si>
+  <si>
+    <t>Ширина фотораздела
+Если не указано 920</t>
   </si>
 </sst>
 </file>
@@ -240,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -250,6 +254,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,16 +552,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="76.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,307 +575,334 @@
       <c r="D1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="E1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="F2" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E3" s="4">
+        <v>767</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D5" s="4"/>
+      <c r="F5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D6" s="4"/>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="D7" s="4"/>
+      <c r="F7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E8" s="5"/>
+      <c r="F8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="F10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="F11" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="F12" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="F13" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="F14" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="F15" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="F16" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="F17" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="C18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="F18" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="F19" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="F20" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="F21" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="4"/>
+      <c r="F22" s="2" t="s">
         <v>47</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/pages.xlsx
+++ b/Assets/StreamingAssets/pages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Work\Encore\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157E0B41-2878-476C-8612-7A0216979750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF26FE2D-2ADA-4DEF-9FB1-CF8924BB1840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6240" yWindow="420" windowWidth="19245" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,12 +171,6 @@
 &lt;br&gt; разбиение на кадры</t>
   </si>
   <si>
-    <t>Корпорация Encore представляет уникальный проект в сфере гостиничного бизнеса и недвижимости на берегу Волги, который объединяет лучшие архитектурные решения, богатую инфраструктуру и атмосферу приватности для роскошной жизни и отдыха в часовой доступности от Москвы.
-•     300 Га общая территория комплекса
-•     3 км береговая линия
-•     86 Га заповедная территория природного парка</t>
-  </si>
-  <si>
     <t>&lt;end&gt;</t>
   </si>
   <si>
@@ -188,6 +182,12 @@
   <si>
     <t>Ширина фотораздела
 Если не указано 920</t>
+  </si>
+  <si>
+    <t>Корпорация Encore представляет уникальный проект в сфере гостиничного бизнеса и недвижимости на берегу Волги, который объединяет лучшие архитектурные решения, богатую инфраструктуру и атмосферу приватности для роскошной жизни и отдыха в часовой доступности от Москвы.
+&lt;line-height=143%&gt;•   300 Га общая территория комплекса
+•   3 км береговая линия
+•   86 Га заповедная территория природного парка</t>
   </si>
 </sst>
 </file>
@@ -576,10 +576,10 @@
         <v>45</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -592,7 +592,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="4"/>
       <c r="F2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -606,13 +606,13 @@
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E3" s="4">
         <v>767</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,7 +630,7 @@
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -645,7 +645,7 @@
       </c>
       <c r="D5" s="4"/>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -660,7 +660,7 @@
       </c>
       <c r="D6" s="4"/>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -675,7 +675,7 @@
       </c>
       <c r="D7" s="4"/>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -693,7 +693,7 @@
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -708,7 +708,7 @@
       </c>
       <c r="D9" s="4"/>
       <c r="F9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -723,7 +723,7 @@
       </c>
       <c r="D10" s="4"/>
       <c r="F10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -738,7 +738,7 @@
       </c>
       <c r="D11" s="4"/>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -753,7 +753,7 @@
       </c>
       <c r="D12" s="4"/>
       <c r="F12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -768,7 +768,7 @@
       </c>
       <c r="D13" s="4"/>
       <c r="F13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -783,7 +783,7 @@
       </c>
       <c r="D14" s="4"/>
       <c r="F14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -798,7 +798,7 @@
       </c>
       <c r="D15" s="4"/>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -813,7 +813,7 @@
       </c>
       <c r="D16" s="4"/>
       <c r="F16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -828,7 +828,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="F17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -843,7 +843,7 @@
       </c>
       <c r="D18" s="4"/>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -858,7 +858,7 @@
       </c>
       <c r="D19" s="4"/>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -873,7 +873,7 @@
       </c>
       <c r="D20" s="4"/>
       <c r="F20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -888,22 +888,22 @@
       </c>
       <c r="D21" s="4"/>
       <c r="F21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="4"/>
       <c r="F22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
